--- a/falkordb_schema.xlsx
+++ b/falkordb_schema.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -461,115 +461,115 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Authority</t>
+          <t>Attribute</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>name, country_code</t>
+          <t>name</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Authority</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>name, iso2, iso3, rtn_code</t>
+          <t>name, country_code</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CountryGroup</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name, iso2, iso3, rtn_code</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DataCategory</t>
+          <t>CountryGroup</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>name, definition, gdpr_category_name</t>
+          <t>name</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DataSubject</t>
+          <t>DataCategory</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>name, definition</t>
+          <t>name, definition, gdpr_category_name</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Duty</t>
+          <t>DataSubject</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>name, module, value</t>
+          <t>name, definition</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Duty</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>name, definition, data_domain, data_privacy_indicator, gdc_level_2, gdc_level_3, category</t>
+          <t>name, module, value</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GlobalBusinessFunction</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>name, rtn_code, gbgf_level_1, privacy_notice, gbgf_level_2</t>
+          <t>name, definition, data_domain, data_privacy_indicator, gdc_level_2, gdc_level_3, category</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LegalEntity</t>
+          <t>GlobalBusinessFunction</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name, rtn_code, gbgf_level_1, privacy_notice, gbgf_level_2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>LegalEntity</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -581,70 +581,94 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Permission</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>name, definition, global_business_function, process_level_indicator, level_1_name, level_2_name, level_3_name, category, l1, l2, l3</t>
+          <t>name</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Purpose</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name, definition, global_business_function, process_level_indicator, level_1_name, level_2_name, level_3_name, category, l1, l2, l3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PurposeOfProcessing</t>
+          <t>Prohibition</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>name, description</t>
+          <t>name</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Regulator</t>
+          <t>Purpose</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>name, country_code, region, regulator, regulator_type, regulator_definition, regulator_address, regulator_original_name, notification_m, notification_nm, approval_m, approval_nm, approval_time, internal_engagement, automated_notification</t>
+          <t>name</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rule</t>
+          <t>PurposeOfProcessing</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rule_id, rule_type, name, description, priority, priority_order, origin_match_type, receiving_match_type, outcome, odrl_type, odrl_action, odrl_target, has_pii_required, requires_any_data, requires_personal_data, enabled</t>
+          <t>name, description</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Regulator</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>name, country_code, region, regulator, regulator_type, regulator_definition, regulator_address, regulator_original_name, notification_m, notification_nm, approval_m, approval_nm, approval_time, internal_engagement, automated_notification</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>rule_id, name, description, priority, outcome, rule_type, enabled, odrl_type, odrl_action, odrl_target, has_pii_required, requires_any_data, requires_personal_data, priority_order, logic_tree, origin_match_type, receiving_match_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>SensitiveDataCategory</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>name, country_code, definition, sensitive_data_category_name</t>
         </is>
@@ -661,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -769,7 +793,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -789,7 +813,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -829,7 +853,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -880,16 +904,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EXCLUDES_RECEIVING</t>
+          <t>HAS_ACTION</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CountryGroup</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -900,16 +924,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HAS_ACTION</t>
+          <t>HAS_ATTRIBUTE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Attribute</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -920,16 +944,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HAS_PERMISSION</t>
+          <t>HAS_DATA_CATEGORY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Permission</t>
+          <t>DataCategory</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -940,16 +964,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LINKED_TO</t>
+          <t>HAS_PERMISSION</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Permission</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -960,16 +984,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LINKED_TO</t>
+          <t>HAS_PROHIBITION</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Regulator</t>
+          <t>Prohibition</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -980,16 +1004,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TRIGGERED_BY_ORIGIN</t>
+          <t>ORIGINATES_FROM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CountryGroup</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1000,7 +1024,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TRIGGERED_BY_ORIGIN</t>
+          <t>RECEIVED_IN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1009,7 +1033,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1020,16 +1044,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>TRIGGERED_BY_ORIGIN</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>TRIGGERED_BY_RECEIVING</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CountryGroup</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>5</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
